--- a/output/Data and Chart Outputs/japan_lng_stock_weekly.xlsx
+++ b/output/Data and Chart Outputs/japan_lng_stock_weekly.xlsx
@@ -193,12 +193,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$10</f>
+              <f>'Chart'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$10</f>
+              <f>'Chart'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -665,7 +665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -744,7 +744,7 @@
         <v>46292</v>
       </c>
       <c r="B9" t="n">
-        <v>2410</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="10">
@@ -752,7 +752,31 @@
         <v>46299</v>
       </c>
       <c r="B10" t="n">
-        <v>2580</v>
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2150</v>
       </c>
     </row>
   </sheetData>
@@ -767,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,7 +867,7 @@
         <v>46292</v>
       </c>
       <c r="B9" t="n">
-        <v>2410</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +875,31 @@
         <v>46299</v>
       </c>
       <c r="B10" t="n">
-        <v>2580</v>
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2150</v>
       </c>
     </row>
   </sheetData>
@@ -901,7 +949,7 @@
         <v>2120</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>46302</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="3">
@@ -915,7 +963,7 @@
         <v>2050</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>46302</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="4">
@@ -929,7 +977,7 @@
         <v>2100</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>46302</v>
+        <v>46323</v>
       </c>
     </row>
   </sheetData>
